--- a/experimental/attention/compressor/tests/pytest/excel/example.xlsx
+++ b/experimental/attention/compressor/tests/pytest/excel/example.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="31">
   <si>
     <t>Testcase_Name</t>
   </si>
@@ -52,6 +52,9 @@
   </si>
   <si>
     <t>rotary_mode</t>
+  </si>
+  <si>
+    <t>cache_mode</t>
   </si>
   <si>
     <t>layout_x</t>
@@ -155,7 +158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -163,9 +166,15 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -174,6 +183,9 @@
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,33 +489,34 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:X3"/>
+  <dimension ref="A1:Y3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="16" max="16" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="24" max="24" style="4" width="10.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="24" max="24" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="25" max="25" style="6" width="10.290714285714287" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
@@ -543,7 +556,7 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
@@ -552,13 +565,13 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
       <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
       <c r="S1" s="1" t="s">
@@ -578,148 +591,157 @@
       </c>
       <c r="X1" s="1" t="s">
         <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="3">
+        <v>25</v>
+      </c>
+      <c r="B2" s="4">
         <v>1</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="4">
         <v>4096</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="4">
         <v>8192</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="4">
         <v>512</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="4">
         <v>128</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="4">
         <v>64</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="4">
         <v>4</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="4">
         <v>2</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="4">
         <v>0.000001</v>
       </c>
-      <c r="K2" s="3">
+      <c r="K2" s="4">
         <v>0</v>
       </c>
       <c r="L2" s="2">
         <v>2</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>25</v>
+      <c r="M2" s="5">
+        <v>1</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="O2" s="1"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>27</v>
       </c>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="4"/>
       <c r="S2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="3">
+        <v>29</v>
+      </c>
+      <c r="B3" s="4">
         <v>1</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="4">
         <v>4096</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="4">
         <v>8192</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="4">
         <v>128</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="4">
         <v>128</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="4">
         <v>64</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="4">
         <v>4</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="4">
         <v>2</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="4">
         <v>0.000001</v>
       </c>
-      <c r="K3" s="3">
+      <c r="K3" s="4">
         <v>0</v>
       </c>
       <c r="L3" s="2">
         <v>2</v>
       </c>
-      <c r="M3" s="1" t="s">
-        <v>25</v>
+      <c r="M3" s="5">
+        <v>2</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>26</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P3" s="2">
+        <v>27</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q3" s="2">
         <v>2</v>
       </c>
-      <c r="Q3" s="3">
+      <c r="R3" s="4">
         <v>8192</v>
       </c>
-      <c r="R3" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="S3" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
